--- a/AncillaryFiles/VDP_Analysis_V3.xlsx
+++ b/AncillaryFiles/VDP_Analysis_V3.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="33940" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="34203" uniqueCount="263">
   <si>
     <t>Participant</t>
   </si>
@@ -800,6 +800,9 @@
   <si>
     <t>AHA-010_V1_FirstVG</t>
   </si>
+  <si>
+    <t>Xe-113</t>
+  </si>
 </sst>
 </file>
 
@@ -844,7 +847,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AK226"/>
+  <dimension ref="A1:AK227"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.42578125" customWidth="true"/>
@@ -26200,19 +26203,19 @@
     </row>
     <row r="225">
       <c r="A225" s="0" t="s">
-        <v>56</v>
+        <v>262</v>
       </c>
       <c r="B225" s="0">
-        <v>13.832287235624833</v>
+        <v>0.078388602978766916</v>
       </c>
       <c r="C225" s="0">
-        <v>13.243299521075647</v>
+        <v>5.4122218056644282</v>
       </c>
       <c r="D225" s="0">
-        <v>69.91700627658625</v>
+        <v>93.892505367915206</v>
       </c>
       <c r="E225" s="0">
-        <v>3.25133117172859</v>
+        <v>0.63733342421867012</v>
       </c>
       <c r="F225" s="0">
         <v>0</v>
@@ -26221,52 +26224,52 @@
         <v>0</v>
       </c>
       <c r="H225" s="0">
-        <v>26.439004075319033</v>
+        <v>2.1403496813332876</v>
       </c>
       <c r="I225" s="0">
-        <v>7.3563970610107985</v>
+        <v>12.709178282948773</v>
       </c>
       <c r="J225" s="0">
-        <v>20.962608204182406</v>
+        <v>44.875771105279298</v>
       </c>
       <c r="K225" s="0">
-        <v>26.572864919534762</v>
+        <v>27.347397839201115</v>
       </c>
       <c r="L225" s="0">
-        <v>15.982984799357469</v>
+        <v>11.001670018063461</v>
       </c>
       <c r="M225" s="0">
-        <v>2.6861409405955321</v>
+        <v>1.925633073174057</v>
       </c>
       <c r="N225" s="0">
-        <v>23.654698515631971</v>
+        <v>0.70890562693841386</v>
       </c>
       <c r="O225" s="0">
-        <v>6.5948775916946785</v>
+        <v>1.9324494734330799</v>
       </c>
       <c r="P225" s="0">
-        <v>42.70755867567005</v>
+        <v>43.246651443372755</v>
       </c>
       <c r="Q225" s="0">
-        <v>27.042865217003303</v>
+        <v>41.157424763982142</v>
       </c>
       <c r="R225" s="0">
-        <v>0</v>
+        <v>12.954568692273611</v>
       </c>
       <c r="S225" s="0">
         <v>0</v>
       </c>
       <c r="T225" s="0">
-        <v>30.359639468126247</v>
+        <v>22.524794655942195</v>
       </c>
       <c r="U225" s="0">
-        <v>29.137043757622632</v>
+        <v>44.517910091680584</v>
       </c>
       <c r="V225" s="0">
-        <v>24.09792664425737</v>
+        <v>22.967860672778706</v>
       </c>
       <c r="W225" s="0">
-        <v>16.405390129993751</v>
+        <v>9.9894345795985142</v>
       </c>
       <c r="X225" s="0">
         <v>0</v>
@@ -26293,16 +26296,16 @@
         <v>0</v>
       </c>
       <c r="AF225" s="0">
-        <v>17.220453936996165</v>
+        <v>0.32718721243311405</v>
       </c>
       <c r="AG225" s="0">
-        <v>13.89475562959217</v>
+        <v>11.95596605432671</v>
       </c>
       <c r="AH225" s="0">
-        <v>30.225778623910522</v>
+        <v>45.707371936880129</v>
       </c>
       <c r="AI225" s="0">
-        <v>29.416664187762144</v>
+        <v>34.235370300944076</v>
       </c>
       <c r="AJ225" s="0">
         <v>0</v>
@@ -26313,19 +26316,19 @@
     </row>
     <row r="226">
       <c r="A226" s="0" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="B226" s="0">
-        <v>0.0071041227592412801</v>
+        <v>13.832287235624833</v>
       </c>
       <c r="C226" s="0">
-        <v>4.8189632716853348</v>
+        <v>13.243299521075647</v>
       </c>
       <c r="D226" s="0">
-        <v>95.375216083733932</v>
+        <v>69.91700627658625</v>
       </c>
       <c r="E226" s="0">
-        <v>0</v>
+        <v>3.25133117172859</v>
       </c>
       <c r="F226" s="0">
         <v>0</v>
@@ -26334,52 +26337,52 @@
         <v>0</v>
       </c>
       <c r="H226" s="0">
-        <v>1.6528925619834711</v>
+        <v>26.439004075319033</v>
       </c>
       <c r="I226" s="0">
-        <v>9.6071420114139574</v>
+        <v>7.3563970610107985</v>
       </c>
       <c r="J226" s="0">
-        <v>30.98344739397097</v>
+        <v>20.962608204182406</v>
       </c>
       <c r="K226" s="0">
-        <v>40.13592554879348</v>
+        <v>26.572864919534762</v>
       </c>
       <c r="L226" s="0">
-        <v>14.894977385209215</v>
+        <v>15.982984799357469</v>
       </c>
       <c r="M226" s="0">
-        <v>2.7256150986289045</v>
+        <v>2.6861409405955321</v>
       </c>
       <c r="N226" s="0">
-        <v>0.86907101754718319</v>
+        <v>23.654698515631971</v>
       </c>
       <c r="O226" s="0">
-        <v>3.2276397736152882</v>
+        <v>6.5948775916946785</v>
       </c>
       <c r="P226" s="0">
-        <v>58.369840630846106</v>
+        <v>42.70755867567005</v>
       </c>
       <c r="Q226" s="0">
-        <v>37.521608373392688</v>
+        <v>27.042865217003303</v>
       </c>
       <c r="R226" s="0">
-        <v>0.011840204598735467</v>
+        <v>0</v>
       </c>
       <c r="S226" s="0">
         <v>0</v>
       </c>
       <c r="T226" s="0">
-        <v>19.010632503729664</v>
+        <v>30.359639468126247</v>
       </c>
       <c r="U226" s="0">
-        <v>38.899808188685505</v>
+        <v>29.137043757622632</v>
       </c>
       <c r="V226" s="0">
-        <v>30.538255701058514</v>
+        <v>24.09792664425737</v>
       </c>
       <c r="W226" s="0">
-        <v>11.551303606526321</v>
+        <v>16.405390129993751</v>
       </c>
       <c r="X226" s="0">
         <v>0</v>
@@ -26406,21 +26409,134 @@
         <v>0</v>
       </c>
       <c r="AF226" s="0">
+        <v>17.220453936996165</v>
+      </c>
+      <c r="AG226" s="0">
+        <v>13.89475562959217</v>
+      </c>
+      <c r="AH226" s="0">
+        <v>30.225778623910522</v>
+      </c>
+      <c r="AI226" s="0">
+        <v>29.416664187762144</v>
+      </c>
+      <c r="AJ226" s="0">
+        <v>0</v>
+      </c>
+      <c r="AK226" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B227" s="0">
+        <v>0.0071041227592412801</v>
+      </c>
+      <c r="C227" s="0">
+        <v>4.8189632716853348</v>
+      </c>
+      <c r="D227" s="0">
+        <v>95.375216083733932</v>
+      </c>
+      <c r="E227" s="0">
+        <v>0</v>
+      </c>
+      <c r="F227" s="0">
+        <v>0</v>
+      </c>
+      <c r="G227" s="0">
+        <v>0</v>
+      </c>
+      <c r="H227" s="0">
+        <v>1.6528925619834711</v>
+      </c>
+      <c r="I227" s="0">
+        <v>9.6071420114139574</v>
+      </c>
+      <c r="J227" s="0">
+        <v>30.98344739397097</v>
+      </c>
+      <c r="K227" s="0">
+        <v>40.13592554879348</v>
+      </c>
+      <c r="L227" s="0">
+        <v>14.894977385209215</v>
+      </c>
+      <c r="M227" s="0">
+        <v>2.7256150986289045</v>
+      </c>
+      <c r="N227" s="0">
+        <v>0.86907101754718319</v>
+      </c>
+      <c r="O227" s="0">
+        <v>3.2276397736152882</v>
+      </c>
+      <c r="P227" s="0">
+        <v>58.369840630846106</v>
+      </c>
+      <c r="Q227" s="0">
+        <v>37.521608373392688</v>
+      </c>
+      <c r="R227" s="0">
+        <v>0.011840204598735467</v>
+      </c>
+      <c r="S227" s="0">
+        <v>0</v>
+      </c>
+      <c r="T227" s="0">
+        <v>19.010632503729664</v>
+      </c>
+      <c r="U227" s="0">
+        <v>38.899808188685505</v>
+      </c>
+      <c r="V227" s="0">
+        <v>30.538255701058514</v>
+      </c>
+      <c r="W227" s="0">
+        <v>11.551303606526321</v>
+      </c>
+      <c r="X227" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y227" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z227" s="0">
+        <v>100</v>
+      </c>
+      <c r="AA227" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB227" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC227" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD227" s="0">
+        <v>0</v>
+      </c>
+      <c r="AE227" s="0">
+        <v>0</v>
+      </c>
+      <c r="AF227" s="0">
         <v>0.33626181060408722</v>
       </c>
-      <c r="AG226" s="0">
+      <c r="AG227" s="0">
         <v>15.662222643207274</v>
       </c>
-      <c r="AH226" s="0">
+      <c r="AH227" s="0">
         <v>45.608468114329014</v>
       </c>
-      <c r="AI226" s="0">
+      <c r="AI227" s="0">
         <v>30.550095905657248</v>
       </c>
-      <c r="AJ226" s="0">
-        <v>0</v>
-      </c>
-      <c r="AK226" s="0">
+      <c r="AJ227" s="0">
+        <v>0</v>
+      </c>
+      <c r="AK227" s="0">
         <v>0</v>
       </c>
     </row>
